--- a/Employee_Reports_wi48/Jerome Latagan Cardejon Q0487.xlsx
+++ b/Employee_Reports_wi48/Jerome Latagan Cardejon Q0487.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-34</v>
+        <v>-37</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-642</v>
+        <v>-645</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
